--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NoguchiTakuya\Documents\Claude\projects\テンプレート作成\03_設計\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hackathon\OnSiteB\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A8B1AD5-631D-459D-BF28-7F489CC436FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CBA7BB-FE77-4CD4-861E-BAAE649BBEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6570" yWindow="-11835" windowWidth="17280" windowHeight="10680" activeTab="3" xr2:uid="{900B833C-72D3-4F3F-95D9-ED43B39E1931}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{900B833C-72D3-4F3F-95D9-ED43B39E1931}"/>
   </bookViews>
   <sheets>
     <sheet name="取引先" sheetId="1" r:id="rId1"/>
     <sheet name="取引先責任者" sheetId="2" r:id="rId2"/>
     <sheet name="商談" sheetId="3" r:id="rId3"/>
     <sheet name="リード" sheetId="4" r:id="rId4"/>
+    <sheet name="購入伝票" sheetId="5" r:id="rId5"/>
+    <sheet name="購入明細" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="239">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -519,6 +521,246 @@
   </si>
   <si>
     <t>商談化時に自動でTrue</t>
+  </si>
+  <si>
+    <t>Store__c</t>
+  </si>
+  <si>
+    <t>担当店舗</t>
+  </si>
+  <si>
+    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ</t>
+  </si>
+  <si>
+    <t>カスタム項目、取引先を担当する店舗（Issue #1）</t>
+  </si>
+  <si>
+    <t>作成日：2026年10月23日</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>購入した商品の名前</t>
+  </si>
+  <si>
+    <t>初期値：1</t>
+  </si>
+  <si>
+    <t>1個あたりの価格（税込）</t>
+  </si>
+  <si>
+    <t>初期値：今日</t>
+  </si>
+  <si>
+    <t>項目定義書　－ 購入伝票オブジェクト（Purchase_Slip__c）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>購入伝票ID</t>
+  </si>
+  <si>
+    <t>伝票番号</t>
+  </si>
+  <si>
+    <t>PS-00001 形式で自動採番</t>
+  </si>
+  <si>
+    <t>Contact__c</t>
+  </si>
+  <si>
+    <t>取引先責任者</t>
+  </si>
+  <si>
+    <t>Purchase_Date__c</t>
+  </si>
+  <si>
+    <t>購入日</t>
+  </si>
+  <si>
+    <t>購入店舗</t>
+  </si>
+  <si>
+    <t>Payment_Method__c</t>
+  </si>
+  <si>
+    <t>支払方法</t>
+  </si>
+  <si>
+    <t>現金/クレジットカード/電子マネー/QRコード決済</t>
+  </si>
+  <si>
+    <t>Total_Amount__c</t>
+  </si>
+  <si>
+    <t>合計金額</t>
+  </si>
+  <si>
+    <t>積み上げ集計（合計）</t>
+  </si>
+  <si>
+    <t>購入明細の金額を合計</t>
+  </si>
+  <si>
+    <t>Total_Quantity__c</t>
+  </si>
+  <si>
+    <t>合計数量</t>
+  </si>
+  <si>
+    <t>購入明細の数量を合計</t>
+  </si>
+  <si>
+    <t>Line_Count__c</t>
+  </si>
+  <si>
+    <t>明細件数</t>
+  </si>
+  <si>
+    <t>積み上げ集計（件数）</t>
+  </si>
+  <si>
+    <t>購入明細の行数</t>
+  </si>
+  <si>
+    <t>Note__c</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>テキストエリア</t>
+  </si>
+  <si>
+    <t>CreatedById</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>項目定義書　－ 購入明細オブジェクト（Purchase_Line__c）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>購入明細ID</t>
+  </si>
+  <si>
+    <t>明細番号</t>
+  </si>
+  <si>
+    <t>PL-00001 形式で自動採番</t>
+  </si>
+  <si>
+    <t>Purchase_Slip__c</t>
+  </si>
+  <si>
+    <t>購入伝票</t>
+  </si>
+  <si>
+    <t>主従関係（購入伝票）</t>
+  </si>
+  <si>
+    <t>購入伝票の画面に関連リストとして表示</t>
+  </si>
+  <si>
+    <t>Product_Name__c</t>
+  </si>
+  <si>
+    <t>品名</t>
+  </si>
+  <si>
+    <t>Weight__c</t>
+  </si>
+  <si>
+    <t>内容量</t>
+  </si>
+  <si>
+    <t>Unit_Price__c</t>
+  </si>
+  <si>
+    <t>単価</t>
+  </si>
+  <si>
+    <t>Quantity__c</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>Amount__c</t>
+  </si>
+  <si>
+    <t>数式（通貨）</t>
+  </si>
+  <si>
+    <t>単価×数量で自動計算。伝票の合計金額に集計</t>
+  </si>
+  <si>
+    <t>参照（Contact）</t>
+  </si>
+  <si>
+    <t>購入したお客様。店頭でお客様が分からない購入は空欄。取引先責任者の画面に関連リストとして表示</t>
+  </si>
+  <si>
+    <t>Order_Type__c</t>
+  </si>
+  <si>
+    <t>注文の種類</t>
+  </si>
+  <si>
+    <t>店頭販売/オンライン単品/オンライン定期便</t>
+  </si>
+  <si>
+    <t>Status__c</t>
+  </si>
+  <si>
+    <t>状態</t>
+  </si>
+  <si>
+    <t>完了/発送準備中/発送済み/キャンセル</t>
+  </si>
+  <si>
+    <t>店頭販売は「完了」</t>
+  </si>
+  <si>
+    <t>Slip_Number__c</t>
+  </si>
+  <si>
+    <t>元データの番号</t>
+  </si>
+  <si>
+    <t>テキスト（外部ID・一意）</t>
+  </si>
+  <si>
+    <t>POSの取引番号、オンラインショップの注文番号など</t>
+  </si>
+  <si>
+    <t>ギフト包装の有無、POSの日時・レジ番号、定期便の頻度など</t>
+  </si>
+  <si>
+    <t>所有者</t>
+  </si>
+  <si>
+    <t>初期値：作成者</t>
+  </si>
+  <si>
+    <t>Product_Code__c</t>
+  </si>
+  <si>
+    <t>商品コード</t>
+  </si>
+  <si>
+    <t>商品マスタの商品コード（例：B001）</t>
+  </si>
+  <si>
+    <t>100g/200g/500g/1箱</t>
+  </si>
+  <si>
+    <t>初期値：200g。ギフトは1箱</t>
+  </si>
+  <si>
+    <t>購入伝票の取引先責任者をフローで自動コピー（フロー：購入明細：取引先責任者のコピー／購入伝票：明細の取引先責任者を同期）。取引先責任者の画面に関連リストとして表示</t>
   </si>
 </sst>
 </file>
@@ -690,12 +932,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -767,6 +1003,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1102,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858D6FC1-04B4-46E2-8A1F-4C11D190D841}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -1115,17 +1357,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
@@ -1139,366 +1381,391 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>255</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>40</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="19" t="s">
+      <c r="F6" s="13"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="9" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17"/>
+      <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19" t="s">
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>40</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19" t="s">
+      <c r="F12" s="13"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <v>255</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="17" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>32000</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="17"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="15"/>
     </row>
     <row r="16" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="20" t="s">
+      <c r="E16" s="18"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" s="25" t="s">
+      <c r="H16" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="23" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="22" t="s">
+      <c r="E17" s="19"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="20" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -1525,17 +1792,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
@@ -1549,288 +1816,288 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="15" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>80</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="19"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>40</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>128</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <v>80</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="15"/>
     </row>
     <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>80</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="7">
         <v>40</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="15"/>
     </row>
     <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>40</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13" t="s">
+      <c r="E14" s="11"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="14"/>
+      <c r="I14" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1856,17 +2123,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
@@ -1880,317 +2147,317 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>120</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="15" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="26" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="19"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="15" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="26" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="19"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="15"/>
     </row>
     <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="17" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="15"/>
     </row>
     <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>32000</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="17"/>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="18">
         <v>255</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="25" t="s">
+      <c r="F14" s="21"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="23" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="21" t="s">
+      <c r="E15" s="19"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="20" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2218,17 +2485,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
@@ -2242,337 +2509,1105 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>80</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17"/>
+      <c r="I5" s="15"/>
     </row>
     <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>40</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="19"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>255</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17"/>
+      <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>128</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <v>80</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="15"/>
     </row>
     <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>40</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="17"/>
+      <c r="I11" s="15"/>
     </row>
     <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12" t="s">
+      <c r="E12" s="10"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="17"/>
     </row>
     <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="10">
         <v>32000</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="19"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="17"/>
+      <c r="I15" s="15"/>
     </row>
     <row r="16" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
+      <c r="E16" s="3"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="4" t="s">
         <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3D4AA0-875E-44B3-BD81-E9BBAE9013D3}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="E12" s="10">
+        <v>50</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E16" s="7">
+        <v>255</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9FEE550-DE28-43B8-BA6F-82A885D3DA73}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7">
+        <v>20</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="10">
+        <v>255</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
